--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20241.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -76,13 +76,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>SAAVEDRA</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>JOSE ARTURO</t>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>UTRERA</t>
+  </si>
+  <si>
+    <t>JUAN SEBASTIAN</t>
+  </si>
+  <si>
+    <t>CARLOS DAVID</t>
   </si>
 </sst>
 </file>
@@ -538,16 +547,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>91.43000000000001</v>
+        <v>97.14</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -626,16 +635,19 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>79.17</v>
+      </c>
+      <c r="H2">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -649,16 +661,19 @@
         <v>36</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>36</v>
       </c>
-      <c r="E3">
-        <v>36</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -672,16 +687,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>97.14</v>
+      </c>
+      <c r="H4">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -695,16 +713,19 @@
         <v>24</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>24</v>
       </c>
-      <c r="E5">
-        <v>24</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -760,16 +781,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>83.33</v>
+        <v>79.17</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -795,7 +816,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -812,16 +833,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>91.43000000000001</v>
+        <v>97.14</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -838,16 +859,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -857,7 +878,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -889,24 +910,47 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920044</v>
+        <v>23330051920008</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>23330051920018</v>
+      </c>
+      <c r="B3" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20241.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="27">
   <si>
     <t>Mat</t>
   </si>
@@ -76,6 +76,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>LUNA</t>
+  </si>
+  <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
@@ -86,6 +89,9 @@
   </si>
   <si>
     <t>UTRERA</t>
+  </si>
+  <si>
+    <t>JUAN YAHEL</t>
   </si>
   <si>
     <t>JUAN SEBASTIAN</t>
@@ -878,7 +884,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -910,16 +916,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920008</v>
+        <v>23330051920015</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -933,7 +939,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920018</v>
+        <v>23330051920008</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
@@ -942,7 +948,7 @@
         <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -951,7 +957,30 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>23330051920018</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20241.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="36">
   <si>
     <t>Mat</t>
   </si>
@@ -76,6 +76,15 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>TELLO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MONTERD</t>
+  </si>
+  <si>
     <t>LUNA</t>
   </si>
   <si>
@@ -85,10 +94,28 @@
     <t>RAMOS</t>
   </si>
   <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
     <t>UTRERA</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>IVONNE ERIMAR</t>
+  </si>
+  <si>
+    <t>ANGEL YAMIL</t>
   </si>
   <si>
     <t>JUAN YAHEL</t>
@@ -884,7 +911,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -916,16 +943,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920015</v>
+        <v>23330051920022</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -934,44 +961,44 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920008</v>
+        <v>23330051920071</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920018</v>
+        <v>23330051920017</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -980,6 +1007,75 @@
         <v>9</v>
       </c>
       <c r="G4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>23330051920015</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>23330051920008</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>23330051920018</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20241.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="37">
   <si>
     <t>Mat</t>
   </si>
@@ -76,52 +76,55 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MONTERD</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
     <t>TELLO</t>
   </si>
   <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>MONTERD</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>UTRERA</t>
   </si>
   <si>
+    <t>ANGEL YAMIL</t>
+  </si>
+  <si>
+    <t>MELANY</t>
+  </si>
+  <si>
+    <t>JUAN YAHEL</t>
+  </si>
+  <si>
     <t>EMMANUEL</t>
   </si>
   <si>
-    <t>IVONNE ERIMAR</t>
-  </si>
-  <si>
-    <t>ANGEL YAMIL</t>
-  </si>
-  <si>
-    <t>JUAN YAHEL</t>
-  </si>
-  <si>
-    <t>JUAN SEBASTIAN</t>
+    <t>ABRIL</t>
   </si>
   <si>
     <t>CARLOS DAVID</t>
@@ -814,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>79.17</v>
+        <v>83.33</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -840,16 +843,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>94.44</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -866,16 +869,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4">
-        <v>97.14</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -901,7 +904,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -943,7 +946,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920022</v>
+        <v>23330051920017</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
@@ -952,7 +955,7 @@
         <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -961,12 +964,12 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920071</v>
+        <v>23330051920105</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
@@ -975,21 +978,21 @@
         <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920017</v>
+        <v>23330051920015</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -998,7 +1001,7 @@
         <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1007,12 +1010,12 @@
         <v>9</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920015</v>
+        <v>23330051920022</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
@@ -1021,7 +1024,7 @@
         <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1035,25 +1038,25 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920008</v>
+        <v>23330051920097</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1064,10 +1067,10 @@
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20241.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20241.xlsx
@@ -76,58 +76,58 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>LUNA</t>
+  </si>
+  <si>
     <t>MONTERD</t>
   </si>
   <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>TELLO</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>TELLO</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>VENTURA</t>
   </si>
   <si>
+    <t>UTRERA</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>OLMOS</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>UTRERA</t>
+    <t>JUAN YAHEL</t>
   </si>
   <si>
     <t>ANGEL YAMIL</t>
   </si>
   <si>
+    <t>CARLOS DAVID</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
     <t>MELANY</t>
-  </si>
-  <si>
-    <t>JUAN YAHEL</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>CARLOS DAVID</t>
   </si>
 </sst>
 </file>
@@ -946,7 +946,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920017</v>
+        <v>23330051920015</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
@@ -969,7 +969,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920105</v>
+        <v>23330051920017</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
@@ -984,7 +984,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -992,7 +992,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920015</v>
+        <v>23330051920018</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -1033,7 +1033,7 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1056,12 +1056,12 @@
         <v>10</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920018</v>
+        <v>23330051920105</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -1076,7 +1076,7 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>1</v>
